--- a/assets/docs/lop2/Giao duc the chat - Lop 2.xlsx
+++ b/assets/docs/lop2/Giao duc the chat - Lop 2.xlsx
@@ -695,8 +695,7 @@
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS chỉ được trên sơ đồ đường di chuyển của tổ mình trong “Chuyển đội hình hàng ngang thành đội hình vòng tròn và ngược lại”.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -730,7 +729,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS chỉ được trên sơ đồ đường di chuyển của tổ mình trong “Chuyển đội hình hàng dọc thành đội hình vòng tròn và ngược lại”.
+          <t>Năng lực số 1.1 CB1b: HS chỉ được trên sơ đồ đường di chuyển của tổ mình trong “Chuyển đội hình hàng ngang thành đội hình vòng tròn và ngược lại”.
 KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
@@ -799,8 +798,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Giậm chân tại chỗ, đứng lại” đã chọn sẵn, cho chạy chậm.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -1005,8 +1003,7 @@
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1b: HS tập “Động tác vươn thở, động tác tay” đúng theo nhịp phát ra và tự nhận ra khi mình lệch nhịp.
-KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
+          <t>KNS: KN hợp tác và tuân thủ luật chơi; thắng không kiêu, thua không nản.</t>
         </is>
       </c>
     </row>
@@ -1264,11 +1261,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần đội hình đội ngũ và một số động tác bài thể dục và nói được mình tiến bộ ở nội dung nào.</t>
-        </is>
-      </c>
+      <c r="H25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -1335,8 +1328,7 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Bài tập phối hợp di chuyển vòng trái, vòng phải” đã chọn sẵn, cho chạy chậm.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -1404,8 +1396,7 @@
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Bài tập phối hợp di chuyển nhanh dần theo vạch kẻ thẳng” mà mình hay làm sai.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -1542,8 +1533,7 @@
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Các động tác quỳ, ngồi cơ bản” đã chọn sẵn, cho chạy chậm.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -1881,8 +1871,7 @@
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 3.1 CB1a: HS xem lại clip mình thực hiện “Động tác di chuyển không bóng” cho chạy chậm và chỉ ra được chỗ mình làm chưa đúng.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -1985,8 +1974,7 @@
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 5.2 CB1b: HS tập “Động tác di chuyển không bóng” đúng theo nhịp phát ra và tự nhận ra khi mình lệch nhịp.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -2055,8 +2043,7 @@
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>NLS-KT (Cơ bản 1): Ở phần Hình thành kiến thức bài “Động tác dẫn bóng” của chủ đề Bóng rổ, GV chiếu trên tivi video mẫu.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -2090,8 +2077,7 @@
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 1.1 CB1b: HS quan sát clip chạy chậm và nói được một chi tiết trong “Động tác dẫn bóng” mà mình hay làm sai.
-KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
+          <t>KNS: KN bảo đảm an toàn khi vận động: khởi động kĩ, tập đúng sức, biết dừng khi mệt.</t>
         </is>
       </c>
     </row>
@@ -2349,11 +2335,7 @@
           <t>54</t>
         </is>
       </c>
-      <c r="H57" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Động tác tung và bắt bóng bằng hai tay” đã chọn sẵn, cho chạy chậm.</t>
-        </is>
-      </c>
+      <c r="H57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -2417,11 +2399,7 @@
           <t>56</t>
         </is>
       </c>
-      <c r="H59" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần kĩ năng vận động với bóng (thể thao tự chọn) và nói được mình tiến bộ ở nội dung nào.</t>
-        </is>
-      </c>
+      <c r="H59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -2451,11 +2429,7 @@
           <t>57</t>
         </is>
       </c>
-      <c r="H60" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.4 CB1a: HS đọc được bảng theo dõi phần kĩ năng vận động với bóng (thể thao tự chọn) và nói được mình tiến bộ ở nội dung nào.</t>
-        </is>
-      </c>
+      <c r="H60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -2613,11 +2587,7 @@
           <t>62</t>
         </is>
       </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>NLS-KT (Cơ bản 1): Chiếu clip mẫu “Động tác ném rổ bằng hai tay trước ngực” đã chọn sẵn, cho chạy chậm.</t>
-        </is>
-      </c>
+      <c r="H65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="4" t="inlineStr">
@@ -2835,11 +2805,7 @@
           <t>69</t>
         </is>
       </c>
-      <c r="H72" s="4" t="inlineStr">
-        <is>
-          <t>Năng lực số 5.2 CB1b: HS chọn và ghi được hai việc rèn luyện ở nhà gắn với các nội dung đã học trong năm.</t>
-        </is>
-      </c>
+      <c r="H72" s="4" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="4" t="inlineStr">
